--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2903-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2903-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64F6706C-F2F3-4008-807C-A70EBF4C460D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83648E60-6579-4080-B1B6-B1E6DE7B9000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{36E0E907-997D-4BF7-8EC2-885DBA15E993}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A84024AF-64A8-4B94-9F14-06E31F2F1C06}"/>
   </bookViews>
   <sheets>
     <sheet name="2903-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1589,26 +1589,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6694E4-FEA5-4455-9742-B95D2A784E73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44751B96-1D97-44BD-A49F-6B503E7825D0}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1641,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1678,7 +1677,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1730,7 +1729,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1798,7 +1797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1942,7 +1941,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2374,7 +2373,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2734,7 +2733,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2806,7 +2805,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2878,7 +2877,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2950,7 +2949,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3022,7 +3021,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3166,7 +3165,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3238,7 +3237,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3310,7 +3309,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1998</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1997</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>1996</v>
       </c>
@@ -3886,7 +3885,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>1995</v>
       </c>
@@ -3958,7 +3957,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="42">
         <v>1994</v>
       </c>
@@ -4030,7 +4029,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="44"/>
       <c r="B36" s="45"/>
       <c r="C36" s="19" t="s">
@@ -4058,7 +4057,7 @@
       <c r="W36" s="51"/>
       <c r="X36" s="47"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>1993</v>
       </c>
@@ -4130,7 +4129,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>1992</v>
       </c>
@@ -4202,7 +4201,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="44"/>
       <c r="B39" s="45"/>
       <c r="C39" s="19" t="s">
@@ -4230,7 +4229,7 @@
       <c r="W39" s="51"/>
       <c r="X39" s="47"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="52">
         <v>1991</v>
       </c>
@@ -4302,7 +4301,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="54"/>
       <c r="B41" s="55"/>
       <c r="C41" s="21" t="s">
@@ -4330,7 +4329,7 @@
       <c r="W41" s="61"/>
       <c r="X41" s="57"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42">
         <v>1990</v>
       </c>
@@ -4402,7 +4401,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="44"/>
       <c r="B43" s="45"/>
       <c r="C43" s="19" t="s">
@@ -4430,7 +4429,7 @@
       <c r="W43" s="51"/>
       <c r="X43" s="47"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <v>1989</v>
       </c>
@@ -4502,7 +4501,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1988</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1987</v>
       </c>
@@ -4646,7 +4645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1986</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1985</v>
       </c>
@@ -4790,7 +4789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1984</v>
       </c>
@@ -4862,7 +4861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>1983</v>
       </c>
@@ -4934,7 +4933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38" t="s">
         <v>64</v>
       </c>
